--- a/data/processed/harmonization/Carbon__Total_carbon/10.15485_2283432/10.15485_2283432_soil_Carbon__Total_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Total_carbon/10.15485_2283432/10.15485_2283432_soil_Carbon__Total_carbon.xlsx
@@ -1844,12 +1844,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>187946:0-20</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>187947:20-40</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>187948:40-60</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>187949:60-100</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>187950:0-20</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>188051:20-40</t>
+          <t>20-40:188051</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>187951:40-60</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>187952:60-100</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>187955:0-20</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>187956:20-40</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>187957:40-60</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>188054:60-100</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>187953:0-20</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>187954:20-40</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>188052:40-60</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>188053:60-100</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
